--- a/examples/wangetal2018/out/ResultFiles/AC_1.0_a.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_1.0_a.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="383">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>a</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,27 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
+    <t>b</t>
   </si>
   <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,28 +133,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -144,6 +178,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -180,6 +217,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -192,6 +235,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -201,27 +247,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -234,39 +301,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -282,6 +340,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -345,12 +406,6 @@
     <t>C_0_3</t>
   </si>
   <si>
-    <t>C_0_4</t>
-  </si>
-  <si>
-    <t>C_0_5</t>
-  </si>
-  <si>
     <t>CS1</t>
   </si>
   <si>
@@ -375,15 +430,6 @@
     <t>C_1_6</t>
   </si>
   <si>
-    <t>C_1_7</t>
-  </si>
-  <si>
-    <t>C_1_8</t>
-  </si>
-  <si>
-    <t>C_1_9</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
@@ -456,351 +502,312 @@
     <t>Erosional velocity (m/s)</t>
   </si>
   <si>
-    <t>PI01_0_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>PI01_0_remaining</t>
-  </si>
-  <si>
-    <t>PI01_1_pre_C_0_1</t>
+    <t>PI01_0</t>
+  </si>
+  <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>PI01_1_pre_C_0_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_0</t>
   </si>
   <si>
     <t>PI01_1_remaining</t>
   </si>
   <si>
-    <t>PI01_pre_C_0_2</t>
+    <t>N_post_C_0_0</t>
+  </si>
+  <si>
+    <t>N01_1</t>
+  </si>
+  <si>
+    <t>PI01_pre_C_0_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_1</t>
   </si>
   <si>
     <t>PI01_remaining</t>
   </si>
   <si>
-    <t>PI02_0_pre_C_0_4</t>
+    <t>N_post_C_0_1</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
+    <t>PI02_0_pre_C_0_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_2</t>
   </si>
   <si>
     <t>PI02_0_remaining</t>
   </si>
   <si>
-    <t>PI02_pre_C_0_5</t>
+    <t>N_post_C_0_2</t>
+  </si>
+  <si>
+    <t>N02_0</t>
+  </si>
+  <si>
+    <t>PI02_pre_C_0_3</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_3</t>
   </si>
   <si>
     <t>PI02_remaining</t>
   </si>
   <si>
-    <t>PI03_0_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI03_0_remaining</t>
-  </si>
-  <si>
-    <t>PI03_pre_C_1_1</t>
+    <t>N_post_C_0_3</t>
+  </si>
+  <si>
+    <t>N03</t>
+  </si>
+  <si>
+    <t>PI03_0</t>
+  </si>
+  <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
+    <t>PI03_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_0</t>
   </si>
   <si>
     <t>PI03_remaining</t>
   </si>
   <si>
-    <t>PI04_0_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>PI04_0_pre_C_1_3</t>
+    <t>N_post_C_1_0</t>
+  </si>
+  <si>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0_pre_C_1_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_1</t>
   </si>
   <si>
     <t>PI04_0_remaining</t>
   </si>
   <si>
-    <t>PI04_1_pre_C_1_4</t>
+    <t>N_post_C_1_1</t>
+  </si>
+  <si>
+    <t>N04_0</t>
+  </si>
+  <si>
+    <t>PI04_1_pre_C_1_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_2</t>
   </si>
   <si>
     <t>PI04_1_remaining</t>
   </si>
   <si>
-    <t>PI04_pre_C_1_5</t>
+    <t>N_post_C_1_2</t>
+  </si>
+  <si>
+    <t>N04_1</t>
+  </si>
+  <si>
+    <t>PI04_pre_C_1_3</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_3</t>
   </si>
   <si>
     <t>PI04_remaining</t>
   </si>
   <si>
-    <t>PI05_0_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>PI05_0_pre_C_1_7</t>
+    <t>N_post_C_1_3</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>PI05_0_pre_C_1_4</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_4</t>
   </si>
   <si>
     <t>PI05_0_remaining</t>
   </si>
   <si>
-    <t>PI05_1_pre_C_1_8</t>
+    <t>N_post_C_1_4</t>
+  </si>
+  <si>
+    <t>N05_0</t>
+  </si>
+  <si>
+    <t>PI05_1_pre_C_1_5</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_5</t>
   </si>
   <si>
     <t>PI05_1_remaining</t>
   </si>
   <si>
-    <t>PI05_pre_C_1_9</t>
+    <t>N_post_C_1_5</t>
+  </si>
+  <si>
+    <t>N05_1</t>
+  </si>
+  <si>
+    <t>PI05_pre_C_1_6</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_6</t>
   </si>
   <si>
     <t>PI05_remaining</t>
   </si>
   <si>
+    <t>N_post_C_1_6</t>
+  </si>
+  <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1_pre_C_2_0</t>
   </si>
   <si>
+    <t>N_pre_C_2_0</t>
+  </si>
+  <si>
     <t>PI06_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_2_0</t>
+  </si>
+  <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
+    <t>N_pre_C_2_1</t>
+  </si>
+  <si>
     <t>PI07_0_remaining</t>
   </si>
   <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>N07_0</t>
+  </si>
+  <si>
     <t>PI07_1_pre_C_2_2</t>
   </si>
   <si>
+    <t>N_pre_C_2_2</t>
+  </si>
+  <si>
     <t>PI07_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_2_2</t>
+  </si>
+  <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1_pre_C_3_0</t>
   </si>
   <si>
+    <t>N_pre_C_3_0</t>
+  </si>
+  <si>
     <t>PI08_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_3_0</t>
+  </si>
+  <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N_pre_C_3_1</t>
+  </si>
+  <si>
     <t>PI09_0_remaining</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1_pre_C_3_2</t>
   </si>
   <si>
+    <t>N_pre_C_3_2</t>
+  </si>
+  <si>
     <t>PI09_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_3_2</t>
+  </si>
+  <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_1</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N_post_C_0_2</t>
-  </si>
-  <si>
-    <t>N_post_C_0_3</t>
-  </si>
-  <si>
-    <t>N_post_C_0_4</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_5</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N_post_C_1_2</t>
-  </si>
-  <si>
-    <t>N_post_C_1_3</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_4</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_5</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N_post_C_1_6</t>
-  </si>
-  <si>
-    <t>N_post_C_1_7</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_8</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_9</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_1</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_2</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_3_1</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_2</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_2</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_4</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_5</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_3</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_4</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_5</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_7</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_8</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_9</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_0</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_2</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_0</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_2</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -868,22 +875,316 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>350811692.4212024</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(65.4655149438955), '2049': np.float64(67.10215281749288), '2050': np.float64(68.77970663793019), '2051': np.float64(70.49919930387846), '2052': np.float64(72.2616792864754), '2053': np.float64(74.06822126863727), '2054': np.float64(75.9199268003532), '2055': np.float64(77.81792497036201), '2056': np.float64(79.76337309462106), '2057': np.float64(81.75745742198659), '2058': np.float64(83.80139385753625), '2059': np.float64(85.89642870397464), '2060': np.float64(88.04383942157399), '2061': np.float64(90.24493540711335), '2062': np.float64(92.50105879229116), '2063': np.float64(94.81358526209844), '2064': np.float64(97.1839248936509), '2065': np.float64(99.61352301599216), '2066': np.float64(102.10386109139195), '2067': np.float64(104.65645761867674), '2068': np.float64(107.27286905914366), '2069': np.float64(109.95469078562223), '2070': np.float64(112.70355805526277), '2071': np.float64(115.52114700664434), '2072': np.float64(118.40917568181044), '2073': np.float64(121.36940507385569), '2074': np.float64(124.40364020070207), '2075': np.float64(127.51373120571961), '2076': np.float64(130.7015744858626), '2077': np.float64(133.96911384800913), '2078': np.float64(137.31834169420938), '2079': np.float64(140.75130023656456), '2080': np.float64(144.27008274247868), '2081': np.float64(147.87683481104065), '2082': np.float64(151.57375568131664), '2020': np.float64(32.790222028526316), '2021': np.float64(33.60997757923947), '2022': np.float64(34.450227018720454), '2023': np.float64(35.31148269418846), '2024': np.float64(36.19426976154317), '2025': np.float64(37.099126505581744), '2026': np.float64(38.02660466822129), '2027': np.float64(38.97726978492682), '2028': np.float64(39.95170152954998), '2029': np.float64(40.95049406778873), '2030': np.float64(41.97425641948344), '2031': np.float64(43.023612829970524), '2032': np.float64(44.09920315071979), '2033': np.float64(45.20168322948777), '2034': np.float64(46.33172531022497), '2035': np.float64(47.490018442980585), '2036': np.float64(48.6772689040551), '2037': np.float64(49.89420062665647), '2038': np.float64(51.14155564232288), '2039': np.float64(52.42009453338094), '2040': np.float64(53.73059689671546), '2041': np.float64(55.07386181913335), '2042': np.float64(56.45070836461168), '2043': np.float64(57.861976073726964), '2044': np.float64(59.30852547557013), '2045': np.float64(60.79123861245938), '2046': np.float64(62.31101957777086), '2047': np.float64(63.868795067215125)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.08058942853044074</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.333333334</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -899,7 +1200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -907,32 +1208,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1246,14 +1529,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1262,28 +1545,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1291,7 +1574,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1299,7 +1582,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1307,15 +1590,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1323,7 +1606,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1331,7 +1614,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1339,7 +1622,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1347,7 +1630,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1355,63 +1638,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>29</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1419,39 +1702,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1461,268 +1805,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
+      <c r="C1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B2">
-        <v>3.260350802924064</v>
+        <v>3.119729578229453</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B4">
-        <v>0.2922816968945701</v>
+        <v>0.2602712666034899</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>0.03718057609316752</v>
+        <v>0.03765058742940535</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B7">
-        <v>0.007683122200429673</v>
+        <v>0.007780246960488626</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>0.01821523095777751</v>
+        <v>0.01844549541147754</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>0.01701801172198347</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B11">
-        <v>2.741131065803681</v>
+        <v>2.642545254665206</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B15">
-        <v>0.02352639978538485</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B16">
-        <v>0.1058166717354106</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B17">
-        <v>0.01749802773165992</v>
+        <v>0.0221064511567996</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.09708815083694389</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.01682411344365728</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B20">
-        <v>32.79022202852632</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>32.79022202852632</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
@@ -1730,472 +2074,307 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B25">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>227223.9994672837</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B27">
-        <v>44106.6807827636</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B28">
-        <v>1837.778365948483</v>
+        <v>212605.6334401885</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>42520.36739708109</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>1771.681974878379</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B31">
-        <v>398937715.3021322</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33">
+        <v>350811692.4212024</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39">
         <v>100</v>
       </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40">
+        <v>0.07843306944639558</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41">
+        <v>0.01510466188011069</v>
+      </c>
+      <c r="C41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52">
-        <v>8.225388745590857</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>11030.41081561225</v>
-      </c>
-      <c r="E52">
-        <v>18900265.89965902</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>78.61647355998096</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53">
-        <v>8.141550848756866</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>10917.98251919993</v>
-      </c>
-      <c r="E53">
-        <v>18771132.20222749</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>77.81516920785451</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54">
-        <v>8.058720607939653</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>10806.90550965923</v>
-      </c>
-      <c r="E54">
-        <v>18643658.74901947</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>77.02349581239781</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55">
-        <v>7.977493021089375</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>10697.97769114127</v>
-      </c>
-      <c r="E55">
-        <v>18518756.15507028</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>76.24714023438588</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56">
-        <v>7.897617543985689</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>10590.86307883569</v>
-      </c>
-      <c r="E56">
-        <v>18396033.51410168</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>75.48370782674692</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57">
-        <v>7.819149184697854</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>10485.63543966352</v>
-      </c>
-      <c r="E57">
-        <v>18275570.16219301</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>74.73372434462227</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" t="s">
         <v>108</v>
       </c>
-      <c r="B58">
-        <v>7.741870496316586</v>
-      </c>
-      <c r="C58">
-        <v>12.5</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G58">
-        <v>73.99511147782827</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" t="s">
+        <v>109</v>
+      </c>
+      <c r="F54" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H54" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59">
-        <v>9.188404909088559</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>12321.83475118594</v>
-      </c>
-      <c r="E59">
-        <v>20391478.33631391</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>87.8207722377832</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60">
-        <v>9.08098389283464</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>12177.78101996911</v>
-      </c>
-      <c r="E60">
-        <v>20224418.73777768</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>86.79406556830945</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H60" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B61">
-        <v>6.633674296063531</v>
+        <v>11.38556858445703</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>8895.889904507116</v>
+        <v>15268.27518312857</v>
       </c>
       <c r="E61">
-        <v>16467389.19048902</v>
+        <v>23848151.84697622</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>63.40321363918</v>
+        <v>108.8207839495881</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2203,25 +2382,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B62">
-        <v>4.985796336893394</v>
+        <v>11.21507652620669</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>6686.052603700778</v>
+        <v>15039.64192317369</v>
       </c>
       <c r="E62">
-        <v>13990499.29065844</v>
+        <v>23577218.83169546</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>47.65315512959055</v>
+        <v>107.1912580020382</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -2229,25 +2408,25 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B63">
-        <v>4.94745737470901</v>
+        <v>11.04904904620964</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>6634.639288632277</v>
+        <v>14816.99575194804</v>
       </c>
       <c r="E63">
-        <v>13933379.38415874</v>
+        <v>23313818.37843499</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>47.2867196819649</v>
+        <v>105.604403520733</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -2255,25 +2434,25 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B64">
-        <v>4.909696785611891</v>
+        <v>10.88744751680322</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>6584.001583441259</v>
+        <v>14600.28486898346</v>
       </c>
       <c r="E64">
-        <v>13877143.69237149</v>
+        <v>23057854.50392316</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64">
-        <v>46.92581219829682</v>
+        <v>104.0598513108886</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -2281,25 +2460,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B65">
-        <v>4.872176912088483</v>
+        <v>10.72998798332667</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D65">
-        <v>6533.686682648897</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>13821288.62304984</v>
+        <v>0</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="G65">
-        <v>46.5672054216374</v>
+        <v>102.5548873957226</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2307,25 +2486,25 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B66">
-        <v>4.835277607086737</v>
+        <v>12.61428890142438</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>6484.203976655456</v>
+        <v>16916.01370258812</v>
       </c>
       <c r="E66">
-        <v>13766378.89844108</v>
+        <v>25814212.2466373</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>46.21452990370442</v>
+        <v>120.56462503713</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2333,25 +2512,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B67">
-        <v>4.798933375006892</v>
+        <v>10.06164143382637</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>6435.465634551742</v>
+        <v>13492.86239558984</v>
       </c>
       <c r="E67">
-        <v>13712316.03442293</v>
+        <v>21756233.1429651</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>45.8671596518249</v>
+        <v>96.16697668866215</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -2359,25 +2538,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B68">
-        <v>4.762945847803322</v>
+        <v>6.65981678835909</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>6387.205640821211</v>
+        <v>8930.947509525307</v>
       </c>
       <c r="E68">
-        <v>13658804.17366352</v>
+        <v>16507026.32353013</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68">
-        <v>45.5231987074373</v>
+        <v>63.65307788486049</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -2385,25 +2564,25 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B69">
-        <v>4.727330793511513</v>
+        <v>6.589442512226696</v>
       </c>
       <c r="C69">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>8836.574197746244</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>16400349.54323283</v>
       </c>
       <c r="F69">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>45.18279777798941</v>
+        <v>62.98045588607278</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -2411,25 +2590,25 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B70">
-        <v>10.96503752972471</v>
+        <v>6.520358239867774</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>14704.33462811143</v>
+        <v>8743.930806827482</v>
       </c>
       <c r="E70">
-        <v>23180699.79078414</v>
+        <v>16295703.70640781</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>104.8014397498095</v>
+        <v>62.32016346229803</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2437,25 +2616,25 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B71">
-        <v>10.76025152729694</v>
+        <v>6.452545336644013</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>14429.71250313574</v>
+        <v>8652.992347346353</v>
       </c>
       <c r="E71">
-        <v>22856674.08461615</v>
+        <v>16193056.42613601</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71">
-        <v>102.844139755454</v>
+        <v>61.67202250772322</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -2463,25 +2642,25 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B72">
-        <v>10.56263850771869</v>
+        <v>6.385955557538513</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>14164.70949162092</v>
+        <v>8563.694121770297</v>
       </c>
       <c r="E72">
-        <v>22544621.02891821</v>
+        <v>16092330.69733595</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72">
-        <v>100.9553975683921</v>
+        <v>61.03557190698792</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -2489,10 +2668,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B73">
-        <v>10.37046637073447</v>
+        <v>6.320557212743167</v>
       </c>
       <c r="C73">
         <v>12.5</v>
@@ -2507,7 +2686,7 @@
         <v>16916025.69007904</v>
       </c>
       <c r="G73">
-        <v>99.11865815175565</v>
+        <v>60.4105087758106</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -2515,25 +2694,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B74">
-        <v>10.18471572868198</v>
+        <v>10.29612970396877</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>13657.9074864771</v>
+        <v>13807.3158556162</v>
       </c>
       <c r="E74">
-        <v>21949543.0340986</v>
+        <v>22124743.04687542</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74">
-        <v>97.34329398462164</v>
+        <v>98.40816448658319</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2541,25 +2720,25 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B75">
-        <v>10.00407428609111</v>
+        <v>10.11666787311622</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>13415.66369913389</v>
+        <v>13566.65395120632</v>
       </c>
       <c r="E75">
-        <v>21665895.26606861</v>
+        <v>21842632.53253276</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>95.61676243279747</v>
+        <v>96.69290740675125</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -2567,27 +2746,131 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B76">
-        <v>9.829186379456615</v>
+        <v>9.943157881954937</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>13181.13551857891</v>
+        <v>13333.97358285921</v>
       </c>
       <c r="E76">
-        <v>21391769.05402897</v>
+        <v>21570358.08697117</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>93.94522192411806</v>
+        <v>95.03453671395744</v>
       </c>
       <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77">
+        <v>9.774600331980468</v>
+      </c>
+      <c r="C77">
+        <v>12.5</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G77">
+        <v>93.42350037503591</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78">
+        <v>9.611372665643923</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>12889.04297208181</v>
+      </c>
+      <c r="E78">
+        <v>21051029.47160658</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>91.86340590270072</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>140</v>
+      </c>
+      <c r="B79">
+        <v>9.452772038358564</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>12676.3563588796</v>
+      </c>
+      <c r="E79">
+        <v>20803388.40424398</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>90.34753566152098</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80">
+        <v>9.298949986516178</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>12470.07791091792</v>
+      </c>
+      <c r="E80">
+        <v>20563585.23169759</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>88.87733800331409</v>
+      </c>
+      <c r="H80">
         <v>0</v>
       </c>
     </row>
@@ -2598,63 +2881,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="R1" s="2" t="s">
+      <c r="A1" t="s">
         <v>142</v>
+      </c>
+      <c r="B1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" t="s">
+        <v>153</v>
+      </c>
+      <c r="O1" t="s">
+        <v>154</v>
+      </c>
+      <c r="P1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>156</v>
+      </c>
+      <c r="R1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2662,55 +2945,55 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F2">
-        <v>49.22791686590655</v>
+        <v>49.09204899863928</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K2">
         <v>4.71984827318464</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="M2">
-        <v>6.21371</v>
+        <v>8.284946666666665</v>
       </c>
       <c r="N2">
         <v>4719848.27318464</v>
       </c>
       <c r="O2">
-        <v>4249638.30898944</v>
+        <v>4099798.606516937</v>
       </c>
       <c r="P2">
-        <v>39.82412088263738</v>
+        <v>44.13251232485468</v>
       </c>
       <c r="Q2">
-        <v>0.03032495478542413</v>
+        <v>0.03402578429493064</v>
       </c>
       <c r="R2">
-        <v>65.37490281132791</v>
+        <v>65.74150433721304</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2718,55 +3001,55 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F3">
-        <v>49.06619074394548</v>
+        <v>49.09205106715859</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K3">
         <v>4.71984827318464</v>
       </c>
       <c r="L3">
-        <v>3.333333333333334</v>
+        <v>0.6666666666666661</v>
       </c>
       <c r="M3">
-        <v>2.071236666666667</v>
+        <v>0.414247333333333</v>
       </c>
       <c r="N3">
-        <v>4719848.27318464</v>
+        <v>4099798.606516937</v>
       </c>
       <c r="O3">
-        <v>4569327.050521234</v>
+        <v>4066445.74913378</v>
       </c>
       <c r="P3">
-        <v>39.4951962850994</v>
+        <v>44.47664867129939</v>
       </c>
       <c r="Q3">
-        <v>0.03004032903136249</v>
+        <v>0.03429850517027516</v>
       </c>
       <c r="R3">
-        <v>63.10924649391834</v>
+        <v>65.99732463733011</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2774,55 +3057,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F4">
-        <v>49.06619146799348</v>
+        <v>48.86725720860368</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>4.71984827318464</v>
       </c>
       <c r="L4">
-        <v>6.666666666666666</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="M4">
-        <v>4.142473333333333</v>
+        <v>7.870699333333335</v>
       </c>
       <c r="N4">
-        <v>4569327.050521234</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O4">
-        <v>4252802.159873962</v>
+        <v>4138468.765097561</v>
       </c>
       <c r="P4">
-        <v>39.54807224605353</v>
+        <v>43.53983594077022</v>
       </c>
       <c r="Q4">
-        <v>0.03011439060324215</v>
+        <v>0.03356057734173422</v>
       </c>
       <c r="R4">
-        <v>65.3512712841131</v>
+        <v>65.44859136435338</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2830,55 +3113,55 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F5">
-        <v>48.90545886978567</v>
+        <v>48.86725740708183</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K5">
         <v>4.71984827318464</v>
       </c>
       <c r="L5">
-        <v>6.666666666666668</v>
+        <v>1.333333333333332</v>
       </c>
       <c r="M5">
-        <v>4.142473333333334</v>
+        <v>0.8284946666666658</v>
       </c>
       <c r="N5">
-        <v>4719848.27318464</v>
+        <v>4138468.765097561</v>
       </c>
       <c r="O5">
-        <v>4415849.20484682</v>
+        <v>4072700.744024519</v>
       </c>
       <c r="P5">
-        <v>39.47151397907326</v>
+        <v>44.20833918006166</v>
       </c>
       <c r="Q5">
-        <v>0.03003815768286931</v>
+        <v>0.03409020938594288</v>
       </c>
       <c r="R5">
-        <v>64.16707856962724</v>
+        <v>65.94912056125608</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2886,55 +3169,55 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F6">
-        <v>48.90545894727407</v>
+        <v>48.64574949478877</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K6">
         <v>4.71984827318464</v>
       </c>
       <c r="L6">
-        <v>3.333333333333332</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>2.071236666666666</v>
+        <v>7.456452000000001</v>
       </c>
       <c r="N6">
-        <v>4415849.20484682</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O6">
-        <v>4255945.102924068</v>
+        <v>4176117.71785819</v>
       </c>
       <c r="P6">
-        <v>39.49805304429255</v>
+        <v>42.97050669925552</v>
       </c>
       <c r="Q6">
-        <v>0.0300759452852327</v>
+        <v>0.03311393540663566</v>
       </c>
       <c r="R6">
-        <v>65.3278212773733</v>
+        <v>65.16714270066454</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2942,55 +3225,55 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F7">
-        <v>48.74629338687364</v>
+        <v>48.64574950933918</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K7">
         <v>4.71984827318464</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>6.21371</v>
+        <v>1.242742</v>
       </c>
       <c r="N7">
-        <v>4719848.27318464</v>
+        <v>4176117.71785819</v>
       </c>
       <c r="O7">
-        <v>4259033.617799386</v>
+        <v>4078827.875271544</v>
       </c>
       <c r="P7">
-        <v>39.44919414941312</v>
+        <v>43.94509017824954</v>
       </c>
       <c r="Q7">
-        <v>0.03003839102500829</v>
+        <v>0.03388586450992616</v>
       </c>
       <c r="R7">
-        <v>65.30480194242692</v>
+        <v>65.9020041259715</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2998,55 +3281,55 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F8">
-        <v>48.58872617267181</v>
+        <v>48.42751431449597</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K8">
         <v>4.71984827318464</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M8">
-        <v>6.21371</v>
+        <v>8.077823</v>
       </c>
       <c r="N8">
         <v>4719848.27318464</v>
       </c>
       <c r="O8">
-        <v>4262080.743589859</v>
+        <v>4133250.983622014</v>
       </c>
       <c r="P8">
-        <v>39.3216794099889</v>
+        <v>43.1998596248076</v>
       </c>
       <c r="Q8">
-        <v>0.02994095135756903</v>
+        <v>0.03329962044477097</v>
       </c>
       <c r="R8">
-        <v>65.28211491898304</v>
+        <v>65.4878858494308</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -3054,55 +3337,55 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E9" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F9">
-        <v>48.43273616991537</v>
+        <v>48.42751431535664</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K9">
         <v>4.71984827318464</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>3.106855</v>
+        <v>0.621371</v>
       </c>
       <c r="N9">
-        <v>4719848.27318464</v>
+        <v>4133250.983622014</v>
       </c>
       <c r="O9">
-        <v>4498059.16417879</v>
+        <v>4084824.327319812</v>
       </c>
       <c r="P9">
-        <v>39.03758371274426</v>
+        <v>43.68687335809297</v>
       </c>
       <c r="Q9">
-        <v>0.02969942313618904</v>
+        <v>0.03368544803973143</v>
       </c>
       <c r="R9">
-        <v>63.59390019111579</v>
+        <v>65.85599022833188</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -3110,111 +3393,111 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="E10" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F10">
-        <v>48.43273616994023</v>
+        <v>48.21247058665152</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K10">
         <v>4.71984827318464</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M10">
-        <v>3.106855</v>
+        <v>8.699194</v>
       </c>
       <c r="N10">
-        <v>4498059.16417879</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O10">
-        <v>4265082.431988919</v>
+        <v>4090700.505646945</v>
       </c>
       <c r="P10">
-        <v>39.07686715799642</v>
+        <v>43.43346588700003</v>
       </c>
       <c r="Q10">
-        <v>0.02975420590070161</v>
+        <v>0.03348878465181783</v>
       </c>
       <c r="R10">
-        <v>65.25978929686157</v>
+        <v>65.81099262798911</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="E11" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F11">
-        <v>48.2782960091499</v>
+        <v>48.00053690440507</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K11">
         <v>4.71984827318464</v>
       </c>
       <c r="L11">
-        <v>10</v>
+        <v>15.75</v>
       </c>
       <c r="M11">
-        <v>6.21371</v>
+        <v>9.786593249999999</v>
       </c>
       <c r="N11">
         <v>4719848.27318464</v>
       </c>
       <c r="O11">
-        <v>4268050.030515389</v>
+        <v>4012092.760614774</v>
       </c>
       <c r="P11">
-        <v>39.07045583764644</v>
+        <v>44.047486673652</v>
       </c>
       <c r="Q11">
-        <v>0.02974899189762505</v>
+        <v>0.03397972814954381</v>
       </c>
       <c r="R11">
-        <v>65.23773972581979</v>
+        <v>66.42069421168968</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -3222,55 +3505,55 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F12">
-        <v>48.1253822192728</v>
+        <v>48.00053690440708</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K12">
         <v>4.71984827318464</v>
       </c>
       <c r="L12">
-        <v>11.81818181818182</v>
+        <v>0.5</v>
       </c>
       <c r="M12">
-        <v>7.343475454545456</v>
+        <v>0.3106855</v>
       </c>
       <c r="N12">
-        <v>4719848.27318464</v>
+        <v>4012092.760614774</v>
       </c>
       <c r="O12">
-        <v>4184338.016808275</v>
+        <v>3987676.373505829</v>
       </c>
       <c r="P12">
-        <v>39.00422324104421</v>
+        <v>44.30364679384697</v>
       </c>
       <c r="Q12">
-        <v>0.02970807849373306</v>
+        <v>0.03418293971930191</v>
       </c>
       <c r="R12">
-        <v>65.86844341006531</v>
+        <v>66.6135504795686</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -3278,55 +3561,55 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D13" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F13">
-        <v>47.94389716100168</v>
+        <v>47.75138539456847</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K13">
         <v>4.71984827318464</v>
       </c>
       <c r="L13">
-        <v>3.93181818181818</v>
+        <v>15.25</v>
       </c>
       <c r="M13">
-        <v>2.443117795454544</v>
+        <v>9.475907749999999</v>
       </c>
       <c r="N13">
         <v>4719848.27318464</v>
       </c>
       <c r="O13">
-        <v>4549776.475029824</v>
+        <v>4043803.689133783</v>
       </c>
       <c r="P13">
-        <v>38.61043449252709</v>
+        <v>43.49225734349392</v>
       </c>
       <c r="Q13">
-        <v>0.02936929536199399</v>
+        <v>0.0335443557964806</v>
       </c>
       <c r="R13">
-        <v>63.24109524507858</v>
+        <v>66.17270347670936</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -3334,55 +3617,55 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="E14" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F14">
-        <v>47.94389716100155</v>
+        <v>39.63872512177027</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K14">
         <v>4.71984827318464</v>
       </c>
       <c r="L14">
-        <v>7.88636363636364</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>4.900357659090911</v>
+        <v>0.621371</v>
       </c>
       <c r="N14">
-        <v>4549776.475029824</v>
+        <v>4043803.689133783</v>
       </c>
       <c r="O14">
-        <v>4188497.183850276</v>
+        <v>4010355.723012357</v>
       </c>
       <c r="P14">
-        <v>38.67166419066007</v>
+        <v>36.38927430668413</v>
       </c>
       <c r="Q14">
-        <v>0.02945430374359226</v>
+        <v>0.02807224844465036</v>
       </c>
       <c r="R14">
-        <v>65.83667449198599</v>
+        <v>66.43435913762333</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3390,55 +3673,55 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D15" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F15">
-        <v>47.76453383218936</v>
+        <v>39.43999230579136</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K15">
         <v>4.71984827318464</v>
       </c>
       <c r="L15">
-        <v>7.86363636363636</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="M15">
-        <v>4.886235590909089</v>
+        <v>9.424126833333336</v>
       </c>
       <c r="N15">
         <v>4719848.27318464</v>
       </c>
       <c r="O15">
-        <v>4375910.529932729</v>
+        <v>4267144.286680805</v>
       </c>
       <c r="P15">
-        <v>38.58793001998763</v>
+        <v>34.13279902474592</v>
       </c>
       <c r="Q15">
-        <v>0.02936993045286984</v>
+        <v>0.02628799871420095</v>
       </c>
       <c r="R15">
-        <v>64.45118792003778</v>
+        <v>64.50352261178686</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -3446,55 +3729,55 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="E16" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F16">
-        <v>39.65187355939091</v>
+        <v>39.4399923057916</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K16">
         <v>4.71984827318464</v>
       </c>
       <c r="L16">
-        <v>3.95454545454546</v>
+        <v>1.083333333333329</v>
       </c>
       <c r="M16">
-        <v>2.457239863636367</v>
+        <v>0.673151916666664</v>
       </c>
       <c r="N16">
-        <v>4375910.529932729</v>
+        <v>4267144.286680805</v>
       </c>
       <c r="O16">
-        <v>4249056.566156982</v>
+        <v>4233052.906208443</v>
       </c>
       <c r="P16">
-        <v>32.05949512541338</v>
+        <v>34.39343052486906</v>
       </c>
       <c r="Q16">
-        <v>0.0244124631588037</v>
+        <v>0.02649462045539577</v>
       </c>
       <c r="R16">
-        <v>65.3792507727217</v>
+        <v>64.74932254108145</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3502,55 +3785,55 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F17">
-        <v>39.52084834031338</v>
+        <v>39.30845073248427</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K17">
         <v>4.71984827318464</v>
       </c>
       <c r="L17">
-        <v>11.81818181818182</v>
+        <v>15.08333333333334</v>
       </c>
       <c r="M17">
-        <v>7.343475454545456</v>
+        <v>9.372345916666671</v>
       </c>
       <c r="N17">
         <v>4719848.27318464</v>
       </c>
       <c r="O17">
-        <v>4361599.508825609</v>
+        <v>4272807.96439346</v>
       </c>
       <c r="P17">
-        <v>32.03049867360566</v>
+        <v>33.97618417009061</v>
       </c>
       <c r="Q17">
-        <v>0.02438021713269818</v>
+        <v>0.02616642030190793</v>
       </c>
       <c r="R17">
-        <v>64.55391356666263</v>
+        <v>64.46295784698385</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3558,55 +3841,55 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E18" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F18">
-        <v>39.42237123273138</v>
+        <v>39.30845073248397</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K18">
         <v>4.71984827318464</v>
       </c>
       <c r="L18">
-        <v>0.3939393939393909</v>
+        <v>1.166666666666657</v>
       </c>
       <c r="M18">
-        <v>0.2447825151515133</v>
+        <v>0.7249328333333274</v>
       </c>
       <c r="N18">
-        <v>4719848.27318464</v>
+        <v>4272807.96439346</v>
       </c>
       <c r="O18">
-        <v>4708388.696778437</v>
+        <v>4236367.818491977</v>
       </c>
       <c r="P18">
-        <v>31.65809290608964</v>
+        <v>34.25328816581308</v>
       </c>
       <c r="Q18">
-        <v>0.02406696848114839</v>
+        <v>0.02638608888500547</v>
       </c>
       <c r="R18">
-        <v>62.19856395928458</v>
+        <v>64.72529850735094</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -3614,55 +3897,55 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="C19" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" t="s">
         <v>204</v>
       </c>
-      <c r="D19" t="s">
-        <v>242</v>
-      </c>
       <c r="E19" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F19">
-        <v>39.42237123273248</v>
+        <v>39.17829915882685</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K19">
         <v>4.71984827318464</v>
       </c>
       <c r="L19">
-        <v>11.42424242424243</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="M19">
-        <v>7.098692939393943</v>
+        <v>9.320565000000007</v>
       </c>
       <c r="N19">
-        <v>4708388.696778437</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O19">
-        <v>4363396.277196881</v>
+        <v>4278389.283102159</v>
       </c>
       <c r="P19">
-        <v>31.73047904016465</v>
+        <v>33.82178021878901</v>
       </c>
       <c r="Q19">
-        <v>0.02415169826010987</v>
+        <v>0.02604656952411027</v>
       </c>
       <c r="R19">
-        <v>64.54098925185069</v>
+        <v>64.423057735829</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -3670,55 +3953,55 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s">
         <v>206</v>
       </c>
       <c r="E20" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F20">
-        <v>39.32465137832495</v>
+        <v>39.17829915882687</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K20">
         <v>4.71984827318464</v>
       </c>
       <c r="L20">
-        <v>4.742424242424242</v>
+        <v>1.249999999999986</v>
       </c>
       <c r="M20">
-        <v>2.946804893939394</v>
+        <v>0.7767137499999913</v>
       </c>
       <c r="N20">
-        <v>4719848.27318464</v>
+        <v>4278389.283102159</v>
       </c>
       <c r="O20">
-        <v>4580729.086936833</v>
+        <v>4239634.837475628</v>
       </c>
       <c r="P20">
-        <v>31.68975680966506</v>
+        <v>34.11492936123842</v>
       </c>
       <c r="Q20">
-        <v>0.0241025411441384</v>
+        <v>0.02627894496936283</v>
       </c>
       <c r="R20">
-        <v>63.03273103849203</v>
+        <v>64.70164771396755</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -3726,55 +4009,55 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="C21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="E21" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F21">
-        <v>39.32465137832486</v>
+        <v>39.04951210527047</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K21">
         <v>4.71984827318464</v>
       </c>
       <c r="L21">
-        <v>7.075757575757578</v>
+        <v>15.41666666666669</v>
       </c>
       <c r="M21">
-        <v>4.396670560606062</v>
+        <v>9.579469583333347</v>
       </c>
       <c r="N21">
-        <v>4580729.086936833</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O21">
-        <v>4365168.370058776</v>
+        <v>4268544.751900677</v>
       </c>
       <c r="P21">
-        <v>31.7348946394796</v>
+        <v>33.78434623683123</v>
       </c>
       <c r="Q21">
-        <v>0.02415490442068939</v>
+        <v>0.02601939551597051</v>
       </c>
       <c r="R21">
-        <v>64.52825003070281</v>
+        <v>64.49348498134164</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -3782,55 +4065,55 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E22" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F22">
-        <v>39.22767735333835</v>
+        <v>39.04951210527087</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K22">
         <v>4.71984827318464</v>
       </c>
       <c r="L22">
-        <v>9.090909090909093</v>
+        <v>0.8333333333333144</v>
       </c>
       <c r="M22">
-        <v>5.648827272727274</v>
+        <v>0.5178091666666549</v>
       </c>
       <c r="N22">
-        <v>4719848.27318464</v>
+        <v>4268544.751900677</v>
       </c>
       <c r="O22">
-        <v>4450796.311878185</v>
+        <v>4242853.971684759</v>
       </c>
       <c r="P22">
-        <v>31.72264640747313</v>
+        <v>33.97832352616475</v>
       </c>
       <c r="Q22">
-        <v>0.02413823624841061</v>
+        <v>0.0261731649121391</v>
       </c>
       <c r="R22">
-        <v>63.92153544658217</v>
+        <v>64.67836891149891</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -3838,55 +4121,55 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D23" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="E23" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F23">
-        <v>39.22767735333844</v>
+        <v>38.92206446032908</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K23">
         <v>4.71984827318464</v>
       </c>
       <c r="L23">
-        <v>2.727272727272734</v>
+        <v>15.83333333333336</v>
       </c>
       <c r="M23">
-        <v>1.694648181818186</v>
+        <v>9.838374166666684</v>
       </c>
       <c r="N23">
-        <v>4450796.311878185</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O23">
-        <v>4366938.928883267</v>
+        <v>4258800.880863022</v>
       </c>
       <c r="P23">
-        <v>31.74016371074411</v>
+        <v>33.74715295274969</v>
       </c>
       <c r="Q23">
-        <v>0.02415876039681305</v>
+        <v>0.02599239326346707</v>
       </c>
       <c r="R23">
-        <v>64.51552936815388</v>
+        <v>64.56342004621717</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -3894,55 +4177,55 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="C24" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D24" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="E24" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F24">
-        <v>39.13144440327181</v>
+        <v>38.92206446032976</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K24">
         <v>4.71984827318464</v>
       </c>
       <c r="L24">
-        <v>11.81818181818181</v>
+        <v>0.416666666666643</v>
       </c>
       <c r="M24">
-        <v>7.343475454545449</v>
+        <v>0.2589045833333186</v>
       </c>
       <c r="N24">
-        <v>4719848.27318464</v>
+        <v>4258800.880863022</v>
       </c>
       <c r="O24">
-        <v>4368681.271126278</v>
+        <v>4246027.321991217</v>
       </c>
       <c r="P24">
-        <v>31.71489810295234</v>
+        <v>33.84342478318199</v>
       </c>
       <c r="Q24">
-        <v>0.02413937782431743</v>
+        <v>0.02606871278729473</v>
       </c>
       <c r="R24">
-        <v>64.50301877021172</v>
+        <v>64.65544576536435</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -3950,279 +4233,279 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="C25" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D25" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E25" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F25">
-        <v>39.03594027094726</v>
+        <v>38.79593206542956</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K25">
         <v>4.71984827318464</v>
       </c>
       <c r="L25">
-        <v>2.121212121212125</v>
+        <v>16.25000000000003</v>
       </c>
       <c r="M25">
-        <v>1.318059696969699</v>
+        <v>10.09727875000002</v>
       </c>
       <c r="N25">
         <v>4719848.27318464</v>
       </c>
       <c r="O25">
-        <v>4659001.675815244</v>
+        <v>4249155.898450844</v>
       </c>
       <c r="P25">
-        <v>31.39105877335374</v>
+        <v>33.71019677960325</v>
       </c>
       <c r="Q25">
-        <v>0.02386835866571347</v>
+        <v>0.02596556020459877</v>
       </c>
       <c r="R25">
-        <v>62.51719274154135</v>
+        <v>64.63286989244958</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>167</v>
+        <v>220</v>
       </c>
       <c r="C26" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D26" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="E26" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F26">
-        <v>39.03594027094729</v>
+        <v>38.67109138792097</v>
       </c>
       <c r="G26">
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K26">
         <v>4.71984827318464</v>
       </c>
       <c r="L26">
-        <v>9.696969696969688</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M26">
-        <v>6.025415757575752</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N26">
-        <v>4659001.675815244</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O26">
-        <v>4370399.571217718</v>
+        <v>4239608.078025237</v>
       </c>
       <c r="P26">
-        <v>31.45212185468741</v>
+        <v>33.6734742160049</v>
       </c>
       <c r="Q26">
-        <v>0.02393922071176174</v>
+        <v>0.02593889383867995</v>
       </c>
       <c r="R26">
-        <v>64.49068792826782</v>
+        <v>64.70184132723752</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="C27" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D27" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="E27" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F27">
-        <v>38.94115399282509</v>
+        <v>38.671091387921</v>
       </c>
       <c r="G27">
         <v>650</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I27">
         <v>9.525</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K27">
         <v>4.71984827318464</v>
       </c>
       <c r="L27">
-        <v>6.969696969696983</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M27">
-        <v>4.330767575757585</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N27">
-        <v>4719848.27318464</v>
+        <v>4239608.078025237</v>
       </c>
       <c r="O27">
-        <v>4517919.910199916</v>
+        <v>3978974.684979098</v>
       </c>
       <c r="P27">
-        <v>31.43702592230761</v>
+        <v>35.76686344308376</v>
       </c>
       <c r="Q27">
-        <v>0.02391536847839657</v>
+        <v>0.02759791954389148</v>
       </c>
       <c r="R27">
-        <v>63.45771706148315</v>
+        <v>66.68268911924889</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D28" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="E28" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F28">
-        <v>38.94115399282496</v>
+        <v>38.46772706976115</v>
       </c>
       <c r="G28">
         <v>650</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I28">
         <v>9.525</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K28">
         <v>4.71984827318464</v>
       </c>
       <c r="L28">
-        <v>4.848484848484844</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="M28">
-        <v>3.012707878787876</v>
+        <v>5.178091666666668</v>
       </c>
       <c r="N28">
-        <v>4517919.910199916</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O28">
-        <v>4372107.38504912</v>
+        <v>4488278.809916194</v>
       </c>
       <c r="P28">
-        <v>31.46780002604191</v>
+        <v>31.7316135367276</v>
       </c>
       <c r="Q28">
-        <v>0.02395100638173503</v>
+        <v>0.02440527304326021</v>
       </c>
       <c r="R28">
-        <v>64.4784393421604</v>
+        <v>62.97435190807715</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="C29" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D29" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="E29" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F29">
-        <v>38.84707852343799</v>
+        <v>38.46772706976117</v>
       </c>
       <c r="G29">
         <v>650</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I29">
         <v>9.525</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K29">
         <v>4.71984827318464</v>
       </c>
       <c r="L29">
-        <v>11.81818181818183</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M29">
-        <v>7.343475454545462</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N29">
-        <v>4719848.27318464</v>
+        <v>4488278.809916194</v>
       </c>
       <c r="O29">
-        <v>4373803.372732345</v>
+        <v>3987181.233873963</v>
       </c>
       <c r="P29">
-        <v>31.48442782411611</v>
+        <v>35.50921960185364</v>
       </c>
       <c r="Q29">
-        <v>0.02396351581050469</v>
+        <v>0.02739759946216085</v>
       </c>
       <c r="R29">
-        <v>64.46628247830948</v>
+        <v>66.61747880695692</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -4230,31 +4513,31 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D30" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E30" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F30">
-        <v>38.75370650587612</v>
+        <v>38.26790739739702</v>
       </c>
       <c r="G30">
         <v>650</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I30">
         <v>9.525</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K30">
         <v>4.71984827318464</v>
@@ -4269,16 +4552,16 @@
         <v>4719848.27318464</v>
       </c>
       <c r="O30">
-        <v>4226315.523689216</v>
+        <v>4249776.370976392</v>
       </c>
       <c r="P30">
-        <v>31.53328387852071</v>
+        <v>33.24678671838616</v>
       </c>
       <c r="Q30">
-        <v>0.02401384708229597</v>
+        <v>0.02560851105891365</v>
       </c>
       <c r="R30">
-        <v>65.54990070157341</v>
+        <v>64.62839535925006</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -4286,55 +4569,55 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D31" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="E31" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F31">
-        <v>38.75370650587611</v>
+        <v>38.26790739739706</v>
       </c>
       <c r="G31">
         <v>650</v>
       </c>
       <c r="H31" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I31">
         <v>9.525</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K31">
         <v>4.71984827318464</v>
       </c>
       <c r="L31">
-        <v>8.333333333333336</v>
+        <v>8.333333333333329</v>
       </c>
       <c r="M31">
-        <v>5.178091666666668</v>
+        <v>5.178091666666663</v>
       </c>
       <c r="N31">
-        <v>4226315.523689216</v>
+        <v>4249776.370976392</v>
       </c>
       <c r="O31">
-        <v>3957200.863362981</v>
+        <v>3995162.661993316</v>
       </c>
       <c r="P31">
-        <v>31.58725523647256</v>
+        <v>35.25773381361865</v>
       </c>
       <c r="Q31">
-        <v>0.02407773644321705</v>
+        <v>0.02720209941836168</v>
       </c>
       <c r="R31">
-        <v>67.68625407039451</v>
+        <v>66.55424049509776</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -4342,55 +4625,55 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="C32" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="D32" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="E32" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F32">
-        <v>38.53713023450593</v>
+        <v>38.07151481288638</v>
       </c>
       <c r="G32">
         <v>650</v>
       </c>
       <c r="H32" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I32">
         <v>9.525</v>
       </c>
       <c r="J32" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K32">
         <v>4.71984827318464</v>
       </c>
       <c r="L32">
-        <v>8.333333333333332</v>
+        <v>8.333333333333343</v>
       </c>
       <c r="M32">
-        <v>5.178091666666666</v>
+        <v>5.178091666666672</v>
       </c>
       <c r="N32">
         <v>4719848.27318464</v>
       </c>
       <c r="O32">
-        <v>4482360.259830136</v>
+        <v>4492990.596233102</v>
       </c>
       <c r="P32">
-        <v>31.14512730772483</v>
+        <v>31.3734627729908</v>
       </c>
       <c r="Q32">
-        <v>0.02369619668218678</v>
+        <v>0.02412914246466877</v>
       </c>
       <c r="R32">
-        <v>63.70216862348632</v>
+        <v>62.94294236247568</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -4398,31 +4681,31 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D33" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E33" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F33">
-        <v>38.53713023450597</v>
+        <v>38.07151481288635</v>
       </c>
       <c r="G33">
         <v>650</v>
       </c>
       <c r="H33" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I33">
         <v>9.525</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K33">
         <v>4.71984827318464</v>
@@ -4434,219 +4717,219 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N33">
-        <v>4482360.259830136</v>
+        <v>4492990.596233102</v>
       </c>
       <c r="O33">
-        <v>3966230.515163621</v>
+        <v>4002975.713420991</v>
       </c>
       <c r="P33">
-        <v>31.25054854303009</v>
+        <v>35.01175117976895</v>
       </c>
       <c r="Q33">
-        <v>0.02382029995089045</v>
+        <v>0.0270109016425079</v>
       </c>
       <c r="R33">
-        <v>67.61109243631881</v>
+        <v>66.49251037067998</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="C34" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="D34" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="E34" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F34">
-        <v>38.32459880007448</v>
+        <v>37.87845149793687</v>
       </c>
       <c r="G34">
         <v>650</v>
       </c>
       <c r="H34" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I34">
         <v>9.525</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K34">
         <v>4.71984827318464</v>
       </c>
       <c r="L34">
-        <v>16.66666666666666</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M34">
-        <v>10.35618333333333</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N34">
         <v>4719848.27318464</v>
       </c>
       <c r="O34">
-        <v>4237440.127799142</v>
+        <v>4259479.954811273</v>
       </c>
       <c r="P34">
-        <v>31.18412566059767</v>
+        <v>32.83732841482804</v>
       </c>
       <c r="Q34">
-        <v>0.02374694055724817</v>
+        <v>0.02529152573695689</v>
       </c>
       <c r="R34">
-        <v>65.46625436621908</v>
+        <v>64.55853872533694</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="C35" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D35" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E35" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F35">
-        <v>38.32459880007445</v>
+        <v>37.87845149793694</v>
       </c>
       <c r="G35">
         <v>650</v>
       </c>
       <c r="H35" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I35">
         <v>9.525</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K35">
         <v>4.71984827318464</v>
       </c>
       <c r="L35">
-        <v>8.333333333333343</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M35">
-        <v>5.178091666666672</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N35">
-        <v>4237440.127799142</v>
+        <v>4259479.954811273</v>
       </c>
       <c r="O35">
-        <v>3974977.616902517</v>
+        <v>4010587.148711848</v>
       </c>
       <c r="P35">
-        <v>31.23749941053527</v>
+        <v>34.77139570673337</v>
       </c>
       <c r="Q35">
-        <v>0.02380960300258679</v>
+        <v>0.02682410597253958</v>
       </c>
       <c r="R35">
-        <v>67.53852095447411</v>
+        <v>66.43253807113906</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="C36" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="D36" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="E36" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F36">
-        <v>38.11597052519338</v>
+        <v>37.68861217919022</v>
       </c>
       <c r="G36">
         <v>650</v>
       </c>
       <c r="H36" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I36">
         <v>9.525</v>
       </c>
       <c r="J36" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K36">
         <v>4.71984827318464</v>
       </c>
       <c r="L36">
-        <v>8.333333333333329</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="M36">
-        <v>5.178091666666663</v>
+        <v>5.178091666666668</v>
       </c>
       <c r="N36">
         <v>4719848.27318464</v>
       </c>
       <c r="O36">
-        <v>4487491.893684486</v>
+        <v>4497495.340009619</v>
       </c>
       <c r="P36">
-        <v>30.80475238401868</v>
+        <v>31.02834111684463</v>
       </c>
       <c r="Q36">
-        <v>0.0234368141680075</v>
+        <v>0.02386307790754903</v>
       </c>
       <c r="R36">
-        <v>63.66671718993356</v>
+        <v>62.9129569002303</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>178</v>
+        <v>248</v>
       </c>
       <c r="C37" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="D37" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E37" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F37">
-        <v>38.11597052519335</v>
+        <v>37.68861217919019</v>
       </c>
       <c r="G37">
         <v>650</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I37">
         <v>9.525</v>
       </c>
       <c r="J37" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K37">
         <v>4.71984827318464</v>
@@ -4658,19 +4941,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N37">
-        <v>4487491.893684486</v>
+        <v>4497495.340009619</v>
       </c>
       <c r="O37">
-        <v>3983542.501035226</v>
+        <v>4018035.828778721</v>
       </c>
       <c r="P37">
-        <v>30.90902150507598</v>
+        <v>34.53618878837742</v>
       </c>
       <c r="Q37">
-        <v>0.02355850886672773</v>
+        <v>0.02664133439692373</v>
       </c>
       <c r="R37">
-        <v>67.46768722430649</v>
+        <v>66.37400498727784</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -4678,31 +4961,31 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="C38" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="D38" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="E38" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F38">
-        <v>37.91113794410505</v>
+        <v>37.50190546554419</v>
       </c>
       <c r="G38">
         <v>650</v>
       </c>
       <c r="H38" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I38">
         <v>9.525</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K38">
         <v>4.71984827318464</v>
@@ -4717,16 +5000,16 @@
         <v>4719848.27318464</v>
       </c>
       <c r="O38">
-        <v>4248020.493977764</v>
+        <v>4268751.879703147</v>
       </c>
       <c r="P38">
-        <v>30.8476990392637</v>
+        <v>32.44391487512373</v>
       </c>
       <c r="Q38">
-        <v>0.02348980455858946</v>
+        <v>0.02498701367967881</v>
       </c>
       <c r="R38">
-        <v>65.38699655256849</v>
+        <v>64.49200082073307</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -4734,55 +5017,55 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="D39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E39" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F39">
-        <v>37.91113794410507</v>
+        <v>37.50190546554418</v>
       </c>
       <c r="G39">
         <v>650</v>
       </c>
       <c r="H39" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I39">
         <v>9.525</v>
       </c>
       <c r="J39" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K39">
         <v>4.71984827318464</v>
       </c>
       <c r="L39">
-        <v>8.333333333333336</v>
+        <v>8.333333333333329</v>
       </c>
       <c r="M39">
-        <v>5.178091666666668</v>
+        <v>5.178091666666663</v>
       </c>
       <c r="N39">
-        <v>4248020.493977764</v>
+        <v>4268751.879703147</v>
       </c>
       <c r="O39">
-        <v>3991855.077515714</v>
+        <v>4025304.123516916</v>
       </c>
       <c r="P39">
-        <v>30.90049697217973</v>
+        <v>34.30613532934021</v>
       </c>
       <c r="Q39">
-        <v>0.02355131145198195</v>
+        <v>0.02646259219621284</v>
       </c>
       <c r="R39">
-        <v>67.39915282407891</v>
+        <v>66.31703829106898</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -4790,55 +5073,55 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D40" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="E40" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F40">
-        <v>37.70997422245762</v>
+        <v>37.318236972821</v>
       </c>
       <c r="G40">
         <v>650</v>
       </c>
       <c r="H40" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I40">
         <v>9.525</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K40">
         <v>4.71984827318464</v>
       </c>
       <c r="L40">
-        <v>8.333333333333332</v>
+        <v>8.333333333333343</v>
       </c>
       <c r="M40">
-        <v>5.178091666666666</v>
+        <v>5.178091666666672</v>
       </c>
       <c r="N40">
         <v>4719848.27318464</v>
       </c>
       <c r="O40">
-        <v>4492382.359707165</v>
+        <v>4501807.223711387</v>
       </c>
       <c r="P40">
-        <v>30.47663229676193</v>
+        <v>30.695430727905</v>
       </c>
       <c r="Q40">
-        <v>0.02318678439661562</v>
+        <v>0.02360644646703492</v>
       </c>
       <c r="R40">
-        <v>63.63298686499764</v>
+        <v>62.88429530024698</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -4846,31 +5129,31 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="D41" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E41" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="F41">
-        <v>37.70997422245765</v>
+        <v>37.31823697282101</v>
       </c>
       <c r="G41">
         <v>650</v>
       </c>
       <c r="H41" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I41">
         <v>9.525</v>
       </c>
       <c r="J41" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K41">
         <v>4.71984827318464</v>
@@ -4882,243 +5165,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N41">
-        <v>4492382.359707165</v>
+        <v>4501807.223711387</v>
       </c>
       <c r="O41">
-        <v>3999991.01514464</v>
+        <v>4032414.643528196</v>
       </c>
       <c r="P41">
-        <v>30.57979078421727</v>
+        <v>34.08091170371465</v>
       </c>
       <c r="Q41">
-        <v>0.02330620440954485</v>
+        <v>0.02628762417618021</v>
       </c>
       <c r="R41">
-        <v>67.33227659306326</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>183</v>
-      </c>
-      <c r="C42" t="s">
-        <v>227</v>
-      </c>
-      <c r="D42" t="s">
-        <v>228</v>
-      </c>
-      <c r="E42" t="s">
-        <v>257</v>
-      </c>
-      <c r="F42">
-        <v>37.51237844574292</v>
-      </c>
-      <c r="G42">
-        <v>650</v>
-      </c>
-      <c r="H42" t="s">
-        <v>86</v>
-      </c>
-      <c r="I42">
-        <v>9.525</v>
-      </c>
-      <c r="J42" t="s">
-        <v>85</v>
-      </c>
-      <c r="K42">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L42">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="M42">
-        <v>10.35618333333333</v>
-      </c>
-      <c r="N42">
-        <v>4719848.27318464</v>
-      </c>
-      <c r="O42">
-        <v>4258096.727613424</v>
-      </c>
-      <c r="P42">
-        <v>30.52323468230721</v>
-      </c>
-      <c r="Q42">
-        <v>0.0232418461782026</v>
-      </c>
-      <c r="R42">
-        <v>65.31178220582974</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43">
-        <v>3</v>
-      </c>
-      <c r="B43" t="s">
-        <v>184</v>
-      </c>
-      <c r="C43" t="s">
-        <v>228</v>
-      </c>
-      <c r="D43" t="s">
-        <v>255</v>
-      </c>
-      <c r="E43" t="s">
-        <v>257</v>
-      </c>
-      <c r="F43">
-        <v>37.51237844574297</v>
-      </c>
-      <c r="G43">
-        <v>650</v>
-      </c>
-      <c r="H43" t="s">
-        <v>86</v>
-      </c>
-      <c r="I43">
-        <v>9.525</v>
-      </c>
-      <c r="J43" t="s">
-        <v>85</v>
-      </c>
-      <c r="K43">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L43">
-        <v>8.333333333333343</v>
-      </c>
-      <c r="M43">
-        <v>5.178091666666672</v>
-      </c>
-      <c r="N43">
-        <v>4258096.727613424</v>
-      </c>
-      <c r="O43">
-        <v>4007901.848329046</v>
-      </c>
-      <c r="P43">
-        <v>30.57547727242994</v>
-      </c>
-      <c r="Q43">
-        <v>0.02330226234867117</v>
-      </c>
-      <c r="R43">
-        <v>67.26744120513416</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
-      <c r="A44">
-        <v>3</v>
-      </c>
-      <c r="B44" t="s">
-        <v>185</v>
-      </c>
-      <c r="C44" t="s">
-        <v>229</v>
-      </c>
-      <c r="D44" t="s">
-        <v>230</v>
-      </c>
-      <c r="E44" t="s">
-        <v>257</v>
-      </c>
-      <c r="F44">
-        <v>37.31823697282096</v>
-      </c>
-      <c r="G44">
-        <v>650</v>
-      </c>
-      <c r="H44" t="s">
-        <v>86</v>
-      </c>
-      <c r="I44">
-        <v>9.525</v>
-      </c>
-      <c r="J44" t="s">
-        <v>85</v>
-      </c>
-      <c r="K44">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L44">
-        <v>8.333333333333329</v>
-      </c>
-      <c r="M44">
-        <v>5.178091666666663</v>
-      </c>
-      <c r="N44">
-        <v>4719848.27318464</v>
-      </c>
-      <c r="O44">
-        <v>4497048.736084362</v>
-      </c>
-      <c r="P44">
-        <v>30.16003616111644</v>
-      </c>
-      <c r="Q44">
-        <v>0.02294554874107988</v>
-      </c>
-      <c r="R44">
-        <v>63.60085205322961</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
-      <c r="A45">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>186</v>
-      </c>
-      <c r="C45" t="s">
-        <v>230</v>
-      </c>
-      <c r="D45" t="s">
-        <v>256</v>
-      </c>
-      <c r="E45" t="s">
-        <v>257</v>
-      </c>
-      <c r="F45">
-        <v>37.31823697282105</v>
-      </c>
-      <c r="G45">
-        <v>650</v>
-      </c>
-      <c r="H45" t="s">
-        <v>86</v>
-      </c>
-      <c r="I45">
-        <v>9.525</v>
-      </c>
-      <c r="J45" t="s">
-        <v>85</v>
-      </c>
-      <c r="K45">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L45">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M45">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N45">
-        <v>4497048.736084362</v>
-      </c>
-      <c r="O45">
-        <v>4015640.993765987</v>
-      </c>
-      <c r="P45">
-        <v>30.26212302168833</v>
-      </c>
-      <c r="Q45">
-        <v>0.02306281639894722</v>
-      </c>
-      <c r="R45">
-        <v>67.20419382902966</v>
+        <v>66.26144988334148</v>
       </c>
     </row>
   </sheetData>
@@ -5128,63 +5187,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="J1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" t="s">
         <v>265</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="L1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M1" t="s">
         <v>266</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" t="s">
         <v>267</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" t="s">
         <v>268</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" t="s">
         <v>269</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>270</v>
+      </c>
+      <c r="R1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -5192,40 +5251,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>231</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>6.21371</v>
+        <v>8.699194</v>
       </c>
       <c r="H2">
-        <v>1.110647055115384</v>
+        <v>1.16068148067389</v>
       </c>
       <c r="I2">
-        <v>78.61647355998096</v>
+        <v>108.8207839495881</v>
       </c>
       <c r="J2">
-        <v>8.225388745590857</v>
+        <v>11.38556858445703</v>
       </c>
       <c r="K2">
-        <v>11030.41081561225</v>
+        <v>15268.27518312857</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>8.225388745590857</v>
+        <v>11.38556858445703</v>
       </c>
       <c r="N2">
         <v>0.78</v>
@@ -5234,13 +5293,13 @@
         <v>0.357</v>
       </c>
       <c r="P2">
-        <v>18900265.89965902</v>
+        <v>23848151.84697622</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>18900265.89965902</v>
+        <v>23848151.84697622</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5248,40 +5307,40 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>12.42742</v>
+        <v>17.398388</v>
       </c>
       <c r="H3">
-        <v>1.109820794796746</v>
+        <v>1.158898865847096</v>
       </c>
       <c r="I3">
-        <v>77.81516920785451</v>
+        <v>107.1912580020382</v>
       </c>
       <c r="J3">
-        <v>8.141550848756866</v>
+        <v>11.21507652620669</v>
       </c>
       <c r="K3">
-        <v>10917.98251919993</v>
+        <v>15039.64192317369</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>8.141550848756866</v>
+        <v>11.21507652620669</v>
       </c>
       <c r="N3">
         <v>0.78</v>
@@ -5290,13 +5349,13 @@
         <v>0.357</v>
       </c>
       <c r="P3">
-        <v>18771132.20222749</v>
+        <v>23577218.83169546</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>18771132.20222749</v>
+        <v>23577218.83169546</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -5304,40 +5363,40 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="E4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G4">
-        <v>18.64113</v>
+        <v>26.097582</v>
       </c>
       <c r="H4">
-        <v>1.109001211021694</v>
+        <v>1.157157991833725</v>
       </c>
       <c r="I4">
-        <v>77.02349581239781</v>
+        <v>105.604403520733</v>
       </c>
       <c r="J4">
-        <v>8.058720607939653</v>
+        <v>11.04904904620964</v>
       </c>
       <c r="K4">
-        <v>10806.90550965923</v>
+        <v>14816.99575194804</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>8.058720607939653</v>
+        <v>11.04904904620964</v>
       </c>
       <c r="N4">
         <v>0.78</v>
@@ -5346,13 +5405,13 @@
         <v>0.357</v>
       </c>
       <c r="P4">
-        <v>18643658.74901947</v>
+        <v>23313818.37843499</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>18643658.74901947</v>
+        <v>23313818.37843499</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -5360,40 +5419,40 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G5">
-        <v>24.85484</v>
+        <v>34.796776</v>
       </c>
       <c r="H5">
-        <v>1.108196998835467</v>
+        <v>1.155459303749664</v>
       </c>
       <c r="I5">
-        <v>76.24714023438588</v>
+        <v>104.0598513108886</v>
       </c>
       <c r="J5">
-        <v>7.977493021089375</v>
+        <v>10.88744751680322</v>
       </c>
       <c r="K5">
-        <v>10697.97769114127</v>
+        <v>14600.28486898346</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>7.977493021089375</v>
+        <v>10.88744751680322</v>
       </c>
       <c r="N5">
         <v>0.78</v>
@@ -5402,54 +5461,51 @@
         <v>0.357</v>
       </c>
       <c r="P5">
-        <v>18518756.15507028</v>
+        <v>23057854.50392316</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>18518756.15507028</v>
+        <v>23057854.50392316</v>
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6">
-        <v>0</v>
-      </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="D6" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E6" t="s">
-        <v>270</v>
+        <v>161</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G6">
-        <v>31.06855</v>
+        <v>43.49597</v>
       </c>
       <c r="H6">
-        <v>1.107404706089452</v>
+        <v>1.153799518363468</v>
       </c>
       <c r="I6">
-        <v>75.48370782674692</v>
+        <v>102.5548873957226</v>
       </c>
       <c r="J6">
-        <v>7.897617543985689</v>
+        <v>10.72998798332667</v>
       </c>
       <c r="K6">
-        <v>10590.86307883569</v>
+        <v>14389.12848540073</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>7.897617543985689</v>
+        <v>12.5</v>
       </c>
       <c r="N6">
         <v>0.78</v>
@@ -5458,54 +5514,54 @@
         <v>0.357</v>
       </c>
       <c r="P6">
-        <v>18396033.51410168</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R6">
-        <v>18396033.51410168</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>236</v>
+        <v>186</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>86.25</v>
       </c>
       <c r="G7">
-        <v>37.28226</v>
+        <v>53.59324875</v>
       </c>
       <c r="H7">
-        <v>1.106625334550369</v>
+        <v>1.183608656044249</v>
       </c>
       <c r="I7">
-        <v>74.73372434462227</v>
+        <v>120.56462503713</v>
       </c>
       <c r="J7">
-        <v>7.819149184697854</v>
+        <v>12.61428890142438</v>
       </c>
       <c r="K7">
-        <v>10485.63543966352</v>
+        <v>16916.01370258812</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>7.819149184697854</v>
+        <v>12.61428890142438</v>
       </c>
       <c r="N7">
         <v>0.78</v>
@@ -5514,51 +5570,54 @@
         <v>0.357</v>
       </c>
       <c r="P7">
-        <v>18275570.16219301</v>
+        <v>25814212.2466373</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>18275570.16219301</v>
+        <v>25814212.2466373</v>
       </c>
     </row>
     <row r="8" spans="1:18">
+      <c r="A8">
+        <v>1</v>
+      </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="F8">
-        <v>70</v>
+        <v>102.5</v>
       </c>
       <c r="G8">
-        <v>43.49597</v>
+        <v>63.6905275</v>
       </c>
       <c r="H8">
-        <v>1.105855891903567</v>
+        <v>1.17691511655713</v>
       </c>
       <c r="I8">
-        <v>73.99511147782827</v>
+        <v>96.16697668866215</v>
       </c>
       <c r="J8">
-        <v>7.741870496316586</v>
+        <v>10.06164143382637</v>
       </c>
       <c r="K8">
-        <v>10382.00317297047</v>
+        <v>13492.86239558984</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>12.5</v>
+        <v>10.06164143382637</v>
       </c>
       <c r="N8">
         <v>0.78</v>
@@ -5567,13 +5626,13 @@
         <v>0.357</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>21756233.1429651</v>
       </c>
       <c r="Q8">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>16916025.69007904</v>
+        <v>21756233.1429651</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -5581,40 +5640,40 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="D9" t="s">
         <v>198</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F9">
-        <v>81.81818181818181</v>
+        <v>118.75</v>
       </c>
       <c r="G9">
-        <v>50.83944545454546</v>
+        <v>73.78780625</v>
       </c>
       <c r="H9">
-        <v>1.127979683817428</v>
+        <v>1.114998649381924</v>
       </c>
       <c r="I9">
-        <v>87.8207722377832</v>
+        <v>63.65307788486049</v>
       </c>
       <c r="J9">
-        <v>9.188404909088559</v>
+        <v>6.65981678835909</v>
       </c>
       <c r="K9">
-        <v>12321.83475118594</v>
+        <v>8930.947509525307</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>9.188404909088559</v>
+        <v>6.65981678835909</v>
       </c>
       <c r="N9">
         <v>0.78</v>
@@ -5623,13 +5682,13 @@
         <v>0.357</v>
       </c>
       <c r="P9">
-        <v>20391478.33631391</v>
+        <v>16507026.32353013</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>20391478.33631391</v>
+        <v>16507026.32353013</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -5637,40 +5696,40 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="D10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F10">
-        <v>93.63636363636364</v>
+        <v>135</v>
       </c>
       <c r="G10">
-        <v>58.18292090909091</v>
+        <v>83.885085</v>
       </c>
       <c r="H10">
-        <v>1.1268596028626</v>
+        <v>1.114126174923302</v>
       </c>
       <c r="I10">
-        <v>86.79406556830945</v>
+        <v>62.98045588607278</v>
       </c>
       <c r="J10">
-        <v>9.08098389283464</v>
+        <v>6.589442512226696</v>
       </c>
       <c r="K10">
-        <v>12177.78101996911</v>
+        <v>8836.574197746244</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>9.08098389283464</v>
+        <v>6.589442512226696</v>
       </c>
       <c r="N10">
         <v>0.78</v>
@@ -5679,13 +5738,13 @@
         <v>0.357</v>
       </c>
       <c r="P10">
-        <v>20224418.73777768</v>
+        <v>16400349.54323283</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>20224418.73777768</v>
+        <v>16400349.54323283</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -5693,40 +5752,40 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F11">
-        <v>105.4545454545455</v>
+        <v>151.25</v>
       </c>
       <c r="G11">
-        <v>65.52639636363637</v>
+        <v>93.98236375</v>
       </c>
       <c r="H11">
-        <v>1.110799114979413</v>
+        <v>1.113267640756283</v>
       </c>
       <c r="I11">
-        <v>63.40321363918</v>
+        <v>62.32016346229803</v>
       </c>
       <c r="J11">
-        <v>6.633674296063531</v>
+        <v>6.520358239867774</v>
       </c>
       <c r="K11">
-        <v>8895.889904507116</v>
+        <v>8743.930806827482</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>6.633674296063531</v>
+        <v>6.520358239867774</v>
       </c>
       <c r="N11">
         <v>0.78</v>
@@ -5735,13 +5794,13 @@
         <v>0.357</v>
       </c>
       <c r="P11">
-        <v>16467389.19048902</v>
+        <v>16295703.70640781</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>16467389.19048902</v>
+        <v>16295703.70640781</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -5749,40 +5808,40 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F12">
-        <v>117.2727272727273</v>
+        <v>167.5</v>
       </c>
       <c r="G12">
-        <v>72.86987181818182</v>
+        <v>104.0796425</v>
       </c>
       <c r="H12">
-        <v>1.082137015018028</v>
+        <v>1.112422983369959</v>
       </c>
       <c r="I12">
-        <v>47.65315512959055</v>
+        <v>61.67202250772322</v>
       </c>
       <c r="J12">
-        <v>4.985796336893394</v>
+        <v>6.452545336644013</v>
       </c>
       <c r="K12">
-        <v>6686.052603700778</v>
+        <v>8652.992347346353</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>4.985796336893394</v>
+        <v>6.452545336644013</v>
       </c>
       <c r="N12">
         <v>0.78</v>
@@ -5791,13 +5850,13 @@
         <v>0.357</v>
       </c>
       <c r="P12">
-        <v>13990499.29065844</v>
+        <v>16193056.42613601</v>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>13990499.29065844</v>
+        <v>16193056.42613601</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -5805,40 +5864,40 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="D13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F13">
-        <v>129.0909090909091</v>
+        <v>183.75</v>
       </c>
       <c r="G13">
-        <v>80.21334727272728</v>
+        <v>114.17692125</v>
       </c>
       <c r="H13">
-        <v>1.081691410392996</v>
+        <v>1.111591592625744</v>
       </c>
       <c r="I13">
-        <v>47.2867196819649</v>
+        <v>61.03557190698792</v>
       </c>
       <c r="J13">
-        <v>4.94745737470901</v>
+        <v>6.385955557538513</v>
       </c>
       <c r="K13">
-        <v>6634.639288632277</v>
+        <v>8563.694121770297</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>4.94745737470901</v>
+        <v>6.385955557538513</v>
       </c>
       <c r="N13">
         <v>0.78</v>
@@ -5847,54 +5906,51 @@
         <v>0.357</v>
       </c>
       <c r="P13">
-        <v>13933379.38415874</v>
+        <v>16092330.69733595</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13">
-        <v>13933379.38415874</v>
+        <v>16092330.69733595</v>
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14">
-        <v>1</v>
-      </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="E14" t="s">
-        <v>270</v>
+        <v>161</v>
       </c>
       <c r="F14">
-        <v>140.9090909090909</v>
+        <v>200</v>
       </c>
       <c r="G14">
-        <v>87.55682272727275</v>
+        <v>124.2742</v>
       </c>
       <c r="H14">
-        <v>1.081252284690473</v>
+        <v>1.110773147886949</v>
       </c>
       <c r="I14">
-        <v>46.92581219829682</v>
+        <v>60.4105087758106</v>
       </c>
       <c r="J14">
-        <v>4.909696785611891</v>
+        <v>6.320557212743167</v>
       </c>
       <c r="K14">
-        <v>6584.001583441259</v>
+        <v>8475.993633432841</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>4.909696785611891</v>
+        <v>12.5</v>
       </c>
       <c r="N14">
         <v>0.78</v>
@@ -5903,54 +5959,54 @@
         <v>0.357</v>
       </c>
       <c r="P14">
-        <v>13877143.69237149</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R14">
-        <v>13877143.69237149</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F15">
-        <v>152.7272727272727</v>
+        <v>225</v>
       </c>
       <c r="G15">
-        <v>94.9002981818182</v>
+        <v>139.808475</v>
       </c>
       <c r="H15">
-        <v>1.080813895052941</v>
+        <v>1.186197110276271</v>
       </c>
       <c r="I15">
-        <v>46.5672054216374</v>
+        <v>98.40816448658319</v>
       </c>
       <c r="J15">
-        <v>4.872176912088483</v>
+        <v>10.29612970396877</v>
       </c>
       <c r="K15">
-        <v>6533.686682648897</v>
+        <v>13807.3158556162</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>4.872176912088483</v>
+        <v>10.29612970396877</v>
       </c>
       <c r="N15">
         <v>0.78</v>
@@ -5959,54 +6015,54 @@
         <v>0.357</v>
       </c>
       <c r="P15">
-        <v>13821288.62304984</v>
+        <v>22124743.04687542</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
-        <v>13821288.62304984</v>
+        <v>22124743.04687542</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="E16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F16">
-        <v>164.5454545454546</v>
+        <v>250</v>
       </c>
       <c r="G16">
-        <v>102.2437736363636</v>
+        <v>155.34275</v>
       </c>
       <c r="H16">
-        <v>1.080382838725112</v>
+        <v>1.183755639970951</v>
       </c>
       <c r="I16">
-        <v>46.21452990370442</v>
+        <v>96.69290740675125</v>
       </c>
       <c r="J16">
-        <v>4.835277607086737</v>
+        <v>10.11666787311622</v>
       </c>
       <c r="K16">
-        <v>6484.203976655456</v>
+        <v>13566.65395120632</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>4.835277607086737</v>
+        <v>10.11666787311622</v>
       </c>
       <c r="N16">
         <v>0.78</v>
@@ -6015,54 +6071,54 @@
         <v>0.357</v>
       </c>
       <c r="P16">
-        <v>13766378.89844108</v>
+        <v>21842632.53253276</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>13766378.89844108</v>
+        <v>21842632.53253276</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D17" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="E17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F17">
-        <v>176.3636363636364</v>
+        <v>275</v>
       </c>
       <c r="G17">
-        <v>109.5872490909091</v>
+        <v>170.877025</v>
       </c>
       <c r="H17">
-        <v>1.079958067053708</v>
+        <v>1.181390764908119</v>
       </c>
       <c r="I17">
-        <v>45.8671596518249</v>
+        <v>95.03453671395744</v>
       </c>
       <c r="J17">
-        <v>4.798933375006892</v>
+        <v>9.943157881954937</v>
       </c>
       <c r="K17">
-        <v>6435.465634551742</v>
+        <v>13333.97358285921</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>4.798933375006892</v>
+        <v>9.943157881954937</v>
       </c>
       <c r="N17">
         <v>0.78</v>
@@ -6071,54 +6127,51 @@
         <v>0.357</v>
       </c>
       <c r="P17">
-        <v>13712316.03442293</v>
+        <v>21570358.08697117</v>
       </c>
       <c r="Q17">
         <v>0</v>
       </c>
       <c r="R17">
-        <v>13712316.03442293</v>
+        <v>21570358.08697117</v>
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18">
-        <v>1</v>
-      </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D18" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>270</v>
+        <v>161</v>
       </c>
       <c r="F18">
-        <v>188.1818181818182</v>
+        <v>300</v>
       </c>
       <c r="G18">
-        <v>116.9307245454546</v>
+        <v>186.4113</v>
       </c>
       <c r="H18">
-        <v>1.07953621846633</v>
+        <v>1.179084913595691</v>
       </c>
       <c r="I18">
-        <v>45.5231987074373</v>
+        <v>93.42350037503591</v>
       </c>
       <c r="J18">
-        <v>4.762945847803322</v>
+        <v>9.774600331980468</v>
       </c>
       <c r="K18">
-        <v>6387.205640821211</v>
+        <v>13107.93453719245</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>4.762945847803322</v>
+        <v>12.5</v>
       </c>
       <c r="N18">
         <v>0.78</v>
@@ -6127,51 +6180,54 @@
         <v>0.357</v>
       </c>
       <c r="P18">
-        <v>13658804.17366352</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R18">
-        <v>13658804.17366352</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="19" spans="1:18">
+      <c r="A19">
+        <v>3</v>
+      </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D19" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="E19" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="F19">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="G19">
-        <v>124.2742</v>
+        <v>201.945575</v>
       </c>
       <c r="H19">
-        <v>1.079117617085772</v>
+        <v>1.176847204205648</v>
       </c>
       <c r="I19">
-        <v>45.18279777798941</v>
+        <v>91.86340590270072</v>
       </c>
       <c r="J19">
-        <v>4.727330793511513</v>
+        <v>9.611372665643923</v>
       </c>
       <c r="K19">
-        <v>6339.445140714809</v>
+        <v>12889.04297208181</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>12.5</v>
+        <v>9.611372665643923</v>
       </c>
       <c r="N19">
         <v>0.78</v>
@@ -6180,54 +6236,54 @@
         <v>0.357</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>21051029.47160658</v>
       </c>
       <c r="Q19">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>16916025.69007904</v>
+        <v>21051029.47160658</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
         <v>249</v>
       </c>
       <c r="D20" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F20">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="G20">
-        <v>139.808475</v>
+        <v>217.47985</v>
       </c>
       <c r="H20">
-        <v>1.19272395719977</v>
+        <v>1.174665551605903</v>
       </c>
       <c r="I20">
-        <v>104.8014397498095</v>
+        <v>90.34753566152098</v>
       </c>
       <c r="J20">
-        <v>10.96503752972471</v>
+        <v>9.452772038358564</v>
       </c>
       <c r="K20">
-        <v>14704.33462811143</v>
+        <v>12676.3563588796</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>10.96503752972471</v>
+        <v>9.452772038358564</v>
       </c>
       <c r="N20">
         <v>0.78</v>
@@ -6236,54 +6292,54 @@
         <v>0.357</v>
       </c>
       <c r="P20">
-        <v>23180699.79078414</v>
+        <v>20803388.40424398</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
       <c r="R20">
-        <v>23180699.79078414</v>
+        <v>20803388.40424398</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C21" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="E21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F21">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G21">
-        <v>155.34275</v>
+        <v>233.014125</v>
       </c>
       <c r="H21">
-        <v>1.190008562321277</v>
+        <v>1.172544515483938</v>
       </c>
       <c r="I21">
-        <v>102.844139755454</v>
+        <v>88.87733800331409</v>
       </c>
       <c r="J21">
-        <v>10.76025152729694</v>
+        <v>9.298949986516178</v>
       </c>
       <c r="K21">
-        <v>14429.71250313574</v>
+        <v>12470.07791091792</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>10.76025152729694</v>
+        <v>9.298949986516178</v>
       </c>
       <c r="N21">
         <v>0.78</v>
@@ -6292,290 +6348,13 @@
         <v>0.357</v>
       </c>
       <c r="P21">
-        <v>22856674.08461615</v>
+        <v>20563585.23169759</v>
       </c>
       <c r="Q21">
         <v>0</v>
       </c>
       <c r="R21">
-        <v>22856674.08461615</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22">
-        <v>2</v>
-      </c>
-      <c r="B22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D22" t="s">
-        <v>221</v>
-      </c>
-      <c r="E22" t="s">
-        <v>270</v>
-      </c>
-      <c r="F22">
-        <v>275.0000000000001</v>
-      </c>
-      <c r="G22">
-        <v>170.877025</v>
-      </c>
-      <c r="H22">
-        <v>1.187389899534217</v>
-      </c>
-      <c r="I22">
-        <v>100.9553975683921</v>
-      </c>
-      <c r="J22">
-        <v>10.56263850771869</v>
-      </c>
-      <c r="K22">
-        <v>14164.70949162092</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>10.56263850771869</v>
-      </c>
-      <c r="N22">
-        <v>0.78</v>
-      </c>
-      <c r="O22">
-        <v>0.357</v>
-      </c>
-      <c r="P22">
-        <v>22544621.02891821</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>22544621.02891821</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="B23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" t="s">
-        <v>252</v>
-      </c>
-      <c r="D23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E23" t="s">
-        <v>257</v>
-      </c>
-      <c r="F23">
-        <v>300.0000000000001</v>
-      </c>
-      <c r="G23">
-        <v>186.4113</v>
-      </c>
-      <c r="H23">
-        <v>1.184836931439307</v>
-      </c>
-      <c r="I23">
-        <v>99.11865815175565</v>
-      </c>
-      <c r="J23">
-        <v>10.37046637073447</v>
-      </c>
-      <c r="K23">
-        <v>13907.00281248234</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>12.5</v>
-      </c>
-      <c r="N23">
-        <v>0.78</v>
-      </c>
-      <c r="O23">
-        <v>0.357</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R23">
-        <v>16916025.69007904</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" t="s">
-        <v>253</v>
-      </c>
-      <c r="D24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E24" t="s">
-        <v>270</v>
-      </c>
-      <c r="F24">
-        <v>325.0000000000001</v>
-      </c>
-      <c r="G24">
-        <v>201.945575</v>
-      </c>
-      <c r="H24">
-        <v>1.182369645573903</v>
-      </c>
-      <c r="I24">
-        <v>97.34329398462164</v>
-      </c>
-      <c r="J24">
-        <v>10.18471572868198</v>
-      </c>
-      <c r="K24">
-        <v>13657.9074864771</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>10.18471572868198</v>
-      </c>
-      <c r="N24">
-        <v>0.78</v>
-      </c>
-      <c r="O24">
-        <v>0.357</v>
-      </c>
-      <c r="P24">
-        <v>21949543.0340986</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>21949543.0340986</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" t="s">
-        <v>254</v>
-      </c>
-      <c r="D25" t="s">
-        <v>227</v>
-      </c>
-      <c r="E25" t="s">
-        <v>270</v>
-      </c>
-      <c r="F25">
-        <v>350.0000000000001</v>
-      </c>
-      <c r="G25">
-        <v>217.47985</v>
-      </c>
-      <c r="H25">
-        <v>1.179964718749242</v>
-      </c>
-      <c r="I25">
-        <v>95.61676243279747</v>
-      </c>
-      <c r="J25">
-        <v>10.00407428609111</v>
-      </c>
-      <c r="K25">
-        <v>13415.66369913389</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>10.00407428609111</v>
-      </c>
-      <c r="N25">
-        <v>0.78</v>
-      </c>
-      <c r="O25">
-        <v>0.357</v>
-      </c>
-      <c r="P25">
-        <v>21665895.26606861</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>21665895.26606861</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26">
-        <v>3</v>
-      </c>
-      <c r="B26" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" t="s">
-        <v>255</v>
-      </c>
-      <c r="D26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E26" t="s">
-        <v>270</v>
-      </c>
-      <c r="F26">
-        <v>375.0000000000001</v>
-      </c>
-      <c r="G26">
-        <v>233.014125</v>
-      </c>
-      <c r="H26">
-        <v>1.177635693636663</v>
-      </c>
-      <c r="I26">
-        <v>93.94522192411806</v>
-      </c>
-      <c r="J26">
-        <v>9.829186379456615</v>
-      </c>
-      <c r="K26">
-        <v>13181.13551857891</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>9.829186379456615</v>
-      </c>
-      <c r="N26">
-        <v>0.78</v>
-      </c>
-      <c r="O26">
-        <v>0.357</v>
-      </c>
-      <c r="P26">
-        <v>21391769.05402897</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>21391769.05402897</v>
+        <v>20563585.23169759</v>
       </c>
     </row>
   </sheetData>
@@ -6585,20 +6364,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>272</v>
+      <c r="A1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="B2">
         <v>4719848.27318464</v>
@@ -6606,95 +6385,95 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="B3">
-        <v>4249638.30898944</v>
+        <v>4099798.606516937</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B4">
-        <v>4719848.27318464</v>
+        <v>4066445.74913378</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B5">
-        <v>4569327.050521234</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="B6">
-        <v>4252802.159873962</v>
+        <v>4138468.765097561</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="B7">
-        <v>4719848.27318464</v>
+        <v>4072700.744024519</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="B8">
-        <v>4415849.20484682</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="B9">
-        <v>4255945.102924068</v>
+        <v>4176117.71785819</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="B10">
-        <v>4719848.27318464</v>
+        <v>4078827.875271544</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="B11">
-        <v>4259033.617799386</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B12">
-        <v>4719848.27318464</v>
+        <v>4133250.983622014</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="B13">
-        <v>4262080.743589859</v>
+        <v>4084824.327319812</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B14">
         <v>4719848.27318464</v>
@@ -6702,39 +6481,39 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B15">
-        <v>4498059.16417879</v>
+        <v>4090700.505646945</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="B16">
-        <v>4265082.431988919</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B17">
-        <v>4719848.27318464</v>
+        <v>4012092.760614774</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B18">
-        <v>4268050.030515389</v>
+        <v>3987676.373505829</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B19">
         <v>4719848.27318464</v>
@@ -6742,231 +6521,231 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="B20">
-        <v>4184338.016808275</v>
+        <v>4043803.689133783</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B21">
-        <v>4719848.27318464</v>
+        <v>4010355.723012357</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B22">
-        <v>4549776.475029824</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="B23">
-        <v>4188497.183850276</v>
+        <v>4267144.286680805</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B24">
-        <v>4719848.27318464</v>
+        <v>4233052.906208443</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B25">
-        <v>4375910.529932729</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="B26">
-        <v>4249056.566156982</v>
+        <v>4272807.96439346</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B27">
-        <v>4719848.27318464</v>
+        <v>4236367.818491977</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>241</v>
+        <v>203</v>
       </c>
       <c r="B28">
-        <v>4361599.508825609</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B29">
-        <v>4719848.27318464</v>
+        <v>4278389.283102159</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B30">
-        <v>4708388.696778437</v>
+        <v>4239634.837475628</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="B31">
-        <v>4363396.277196881</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B32">
-        <v>4719848.27318464</v>
+        <v>4268544.751900677</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B33">
-        <v>4580729.086936833</v>
+        <v>4242853.971684759</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="B34">
-        <v>4365168.370058776</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B35">
-        <v>4719848.27318464</v>
+        <v>4258800.880863022</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B36">
-        <v>4450796.311878185</v>
+        <v>4246027.321991217</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="B37">
-        <v>4366938.928883267</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B38">
-        <v>4719848.27318464</v>
+        <v>4249155.898450844</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="B39">
-        <v>4368681.271126278</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B40">
-        <v>4719848.27318464</v>
+        <v>4239608.078025237</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B41">
-        <v>4659001.675815244</v>
+        <v>3978974.684979098</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="B42">
-        <v>4370399.571217718</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="B43">
-        <v>4719848.27318464</v>
+        <v>4488278.809916194</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B44">
-        <v>4517919.910199916</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B45">
-        <v>4372107.38504912</v>
+        <v>3987181.233873963</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B46">
-        <v>4719848.27318464</v>
+        <v>4249776.370976392</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B47">
-        <v>4373803.372732345</v>
+        <v>3995162.661993316</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B48">
         <v>4719848.27318464</v>
@@ -6974,23 +6753,23 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="B49">
-        <v>4226315.523689216</v>
+        <v>4492990.596233102</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B50">
-        <v>3957200.863362981</v>
+        <v>4002975.713420991</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="B51">
         <v>4719848.27318464</v>
@@ -6998,23 +6777,23 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="B52">
-        <v>4482360.259830136</v>
+        <v>4259479.954811273</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B53">
-        <v>3966230.515163621</v>
+        <v>4010587.148711848</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="B54">
         <v>4719848.27318464</v>
@@ -7022,10 +6801,10 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="B55">
-        <v>4237440.127799142</v>
+        <v>4497495.340009619</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7033,36 +6812,36 @@
         <v>251</v>
       </c>
       <c r="B56">
-        <v>3974977.616902517</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B57">
-        <v>4719848.27318464</v>
+        <v>4018035.828778721</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="B58">
-        <v>4487491.893684486</v>
+        <v>4268751.879703147</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B59">
-        <v>3983542.501035226</v>
+        <v>4025304.123516916</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="B60">
         <v>4719848.27318464</v>
@@ -7070,90 +6849,18 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="B61">
-        <v>4248020.493977764</v>
+        <v>4501807.223711387</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B62">
-        <v>3991855.077515714</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>225</v>
-      </c>
-      <c r="B63">
-        <v>4719848.27318464</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>226</v>
-      </c>
-      <c r="B64">
-        <v>4492382.359707165</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>254</v>
-      </c>
-      <c r="B65">
-        <v>3999991.01514464</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>227</v>
-      </c>
-      <c r="B66">
-        <v>4719848.27318464</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>228</v>
-      </c>
-      <c r="B67">
-        <v>4258096.727613424</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>255</v>
-      </c>
-      <c r="B68">
-        <v>4007901.848329046</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>229</v>
-      </c>
-      <c r="B69">
-        <v>4719848.27318464</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>230</v>
-      </c>
-      <c r="B70">
-        <v>4497048.736084362</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>256</v>
-      </c>
-      <c r="B71">
-        <v>4015640.993765987</v>
+        <v>4032414.643528196</v>
       </c>
     </row>
   </sheetData>
@@ -7167,37 +6874,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" t="s">
         <v>276</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" t="s">
         <v>277</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" t="s">
         <v>278</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" t="s">
         <v>279</v>
+      </c>
+      <c r="F1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B2">
         <v>8.11266027279845</v>
       </c>
       <c r="C2">
-        <v>8.112660272798458</v>
+        <v>8.112660272798202</v>
       </c>
       <c r="D2">
         <v>141.8178946624533</v>
@@ -7206,21 +6913,21 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520400000001</v>
+        <v>1150.520399999965</v>
       </c>
       <c r="G2">
-        <v>8.758443123059551E-14</v>
+        <v>-3.065455093070843E-12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B3">
         <v>21.09291642722411</v>
       </c>
       <c r="C3">
-        <v>21.09291642722414</v>
+        <v>21.09291642722411</v>
       </c>
       <c r="D3">
         <v>141.8178946624533</v>
@@ -7229,21 +6936,21 @@
         <v>2991.353</v>
       </c>
       <c r="F3">
-        <v>2991.353000000003</v>
+        <v>2991.353</v>
       </c>
       <c r="G3">
-        <v>1.010589604635734E-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B4">
         <v>16.2253205455969</v>
       </c>
       <c r="C4">
-        <v>16.22532054559692</v>
+        <v>16.2253205455969</v>
       </c>
       <c r="D4">
         <v>141.8178946624533</v>
@@ -7252,10 +6959,843 @@
         <v>2301.0408</v>
       </c>
       <c r="F4">
-        <v>2301.040800000002</v>
+        <v>2301.0408</v>
       </c>
       <c r="G4">
-        <v>8.758443123059551E-14</v>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7" t="s">
+        <v>297</v>
+      </c>
+      <c r="F7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G7" t="s">
+        <v>297</v>
+      </c>
+      <c r="H7" t="s">
+        <v>300</v>
+      </c>
+      <c r="I7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" t="s">
+        <v>302</v>
+      </c>
+      <c r="C8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F8" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H8" t="s">
+        <v>308</v>
+      </c>
+      <c r="I8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E9" t="s">
+        <v>297</v>
+      </c>
+      <c r="F9" t="s">
+        <v>300</v>
+      </c>
+      <c r="G9" t="s">
+        <v>288</v>
+      </c>
+      <c r="H9" t="s">
+        <v>312</v>
+      </c>
+      <c r="I9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>317</v>
+      </c>
+      <c r="B13" t="s">
+        <v>311</v>
+      </c>
+      <c r="C13" t="s">
+        <v>297</v>
+      </c>
+      <c r="D13" t="s">
+        <v>308</v>
+      </c>
+      <c r="E13" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D14" t="s">
+        <v>319</v>
+      </c>
+      <c r="E14" t="s">
+        <v>297</v>
+      </c>
+      <c r="F14" t="s">
+        <v>308</v>
+      </c>
+      <c r="G14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" t="s">
+        <v>308</v>
+      </c>
+      <c r="E15" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" t="s">
+        <v>311</v>
+      </c>
+      <c r="C16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D16" t="s">
+        <v>308</v>
+      </c>
+      <c r="E16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>322</v>
+      </c>
+      <c r="B17" t="s">
+        <v>311</v>
+      </c>
+      <c r="C17" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>323</v>
+      </c>
+      <c r="B18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>324</v>
+      </c>
+      <c r="B19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C20" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" t="s">
+        <v>326</v>
+      </c>
+      <c r="E20" t="s">
+        <v>327</v>
+      </c>
+      <c r="F20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G20" t="s">
+        <v>329</v>
+      </c>
+      <c r="H20" t="s">
+        <v>330</v>
+      </c>
+      <c r="I20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>331</v>
+      </c>
+      <c r="B21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F21" t="s">
+        <v>328</v>
+      </c>
+      <c r="G21" t="s">
+        <v>329</v>
+      </c>
+      <c r="H21" t="s">
+        <v>330</v>
+      </c>
+      <c r="I21" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>333</v>
+      </c>
+      <c r="B22" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>335</v>
+      </c>
+      <c r="B23" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>337</v>
+      </c>
+      <c r="B24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>338</v>
+      </c>
+      <c r="B25" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>340</v>
+      </c>
+      <c r="B26" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>341</v>
+      </c>
+      <c r="B27" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>342</v>
+      </c>
+      <c r="B28" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>343</v>
+      </c>
+      <c r="B29" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>345</v>
+      </c>
+      <c r="B30" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>347</v>
+      </c>
+      <c r="B31" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>349</v>
+      </c>
+      <c r="B32" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>351</v>
+      </c>
+      <c r="B33" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>352</v>
+      </c>
+      <c r="B34" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>353</v>
+      </c>
+      <c r="B35" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>355</v>
+      </c>
+      <c r="B36" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>357</v>
+      </c>
+      <c r="B37" t="s">
+        <v>358</v>
+      </c>
+      <c r="C37" t="s">
+        <v>288</v>
+      </c>
+      <c r="D37" t="s">
+        <v>359</v>
+      </c>
+      <c r="E37" t="s">
+        <v>327</v>
+      </c>
+      <c r="F37" t="s">
+        <v>360</v>
+      </c>
+      <c r="G37" t="s">
+        <v>292</v>
+      </c>
+      <c r="H37" t="s">
+        <v>361</v>
+      </c>
+      <c r="I37" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>363</v>
+      </c>
+      <c r="B38" t="s">
+        <v>358</v>
+      </c>
+      <c r="C38" t="s">
+        <v>364</v>
+      </c>
+      <c r="D38" t="s">
+        <v>359</v>
+      </c>
+      <c r="E38" t="s">
+        <v>327</v>
+      </c>
+      <c r="F38" t="s">
+        <v>360</v>
+      </c>
+      <c r="G38" t="s">
+        <v>292</v>
+      </c>
+      <c r="H38" t="s">
+        <v>361</v>
+      </c>
+      <c r="I38" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>365</v>
+      </c>
+      <c r="B39" t="s">
+        <v>358</v>
+      </c>
+      <c r="C39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D39" t="s">
+        <v>359</v>
+      </c>
+      <c r="E39" t="s">
+        <v>327</v>
+      </c>
+      <c r="F39" t="s">
+        <v>360</v>
+      </c>
+      <c r="G39" t="s">
+        <v>292</v>
+      </c>
+      <c r="H39" t="s">
+        <v>361</v>
+      </c>
+      <c r="I39" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>367</v>
+      </c>
+      <c r="B40" t="s">
+        <v>358</v>
+      </c>
+      <c r="C40" t="s">
+        <v>288</v>
+      </c>
+      <c r="D40" t="s">
+        <v>359</v>
+      </c>
+      <c r="E40" t="s">
+        <v>327</v>
+      </c>
+      <c r="F40" t="s">
+        <v>360</v>
+      </c>
+      <c r="G40" t="s">
+        <v>292</v>
+      </c>
+      <c r="H40" t="s">
+        <v>361</v>
+      </c>
+      <c r="I40" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>368</v>
+      </c>
+      <c r="B41" t="s">
+        <v>358</v>
+      </c>
+      <c r="C41" t="s">
+        <v>369</v>
+      </c>
+      <c r="D41" t="s">
+        <v>359</v>
+      </c>
+      <c r="E41" t="s">
+        <v>327</v>
+      </c>
+      <c r="F41" t="s">
+        <v>360</v>
+      </c>
+      <c r="G41" t="s">
+        <v>292</v>
+      </c>
+      <c r="H41" t="s">
+        <v>361</v>
+      </c>
+      <c r="I41" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>370</v>
+      </c>
+      <c r="B42" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42" t="s">
+        <v>371</v>
+      </c>
+      <c r="D42" t="s">
+        <v>359</v>
+      </c>
+      <c r="E42" t="s">
+        <v>327</v>
+      </c>
+      <c r="F42" t="s">
+        <v>360</v>
+      </c>
+      <c r="G42" t="s">
+        <v>292</v>
+      </c>
+      <c r="H42" t="s">
+        <v>361</v>
+      </c>
+      <c r="I42" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>372</v>
+      </c>
+      <c r="B43" t="s">
+        <v>358</v>
+      </c>
+      <c r="C43" t="s">
+        <v>297</v>
+      </c>
+      <c r="D43" t="s">
+        <v>359</v>
+      </c>
+      <c r="E43" t="s">
+        <v>327</v>
+      </c>
+      <c r="F43" t="s">
+        <v>360</v>
+      </c>
+      <c r="G43" t="s">
+        <v>292</v>
+      </c>
+      <c r="H43" t="s">
+        <v>361</v>
+      </c>
+      <c r="I43" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>358</v>
+      </c>
+      <c r="C44" t="s">
+        <v>288</v>
+      </c>
+      <c r="D44" t="s">
+        <v>359</v>
+      </c>
+      <c r="E44" t="s">
+        <v>327</v>
+      </c>
+      <c r="F44" t="s">
+        <v>360</v>
+      </c>
+      <c r="G44" t="s">
+        <v>292</v>
+      </c>
+      <c r="H44" t="s">
+        <v>361</v>
+      </c>
+      <c r="I44" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>373</v>
+      </c>
+      <c r="B45" t="s">
+        <v>358</v>
+      </c>
+      <c r="C45" t="s">
+        <v>288</v>
+      </c>
+      <c r="D45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E45" t="s">
+        <v>327</v>
+      </c>
+      <c r="F45" t="s">
+        <v>360</v>
+      </c>
+      <c r="G45" t="s">
+        <v>292</v>
+      </c>
+      <c r="H45" t="s">
+        <v>361</v>
+      </c>
+      <c r="I45" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>374</v>
+      </c>
+      <c r="B46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C46" t="s">
+        <v>375</v>
+      </c>
+      <c r="D46" t="s">
+        <v>376</v>
+      </c>
+      <c r="E46" t="s">
+        <v>377</v>
+      </c>
+      <c r="F46" t="s">
+        <v>308</v>
+      </c>
+      <c r="G46" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>378</v>
+      </c>
+      <c r="B47" t="s">
+        <v>358</v>
+      </c>
+      <c r="C47" t="s">
+        <v>346</v>
+      </c>
+      <c r="D47" t="s">
+        <v>376</v>
+      </c>
+      <c r="E47" t="s">
+        <v>297</v>
+      </c>
+      <c r="F47" t="s">
+        <v>308</v>
+      </c>
+      <c r="G47" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>379</v>
+      </c>
+      <c r="B48" t="s">
+        <v>358</v>
+      </c>
+      <c r="C48" t="s">
+        <v>346</v>
+      </c>
+      <c r="D48" t="s">
+        <v>376</v>
+      </c>
+      <c r="E48" t="s">
+        <v>297</v>
+      </c>
+      <c r="F48" t="s">
+        <v>308</v>
+      </c>
+      <c r="G48" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>380</v>
+      </c>
+      <c r="B49" t="s">
+        <v>358</v>
+      </c>
+      <c r="C49" t="s">
+        <v>375</v>
+      </c>
+      <c r="D49" t="s">
+        <v>376</v>
+      </c>
+      <c r="E49" t="s">
+        <v>297</v>
+      </c>
+      <c r="F49" t="s">
+        <v>308</v>
+      </c>
+      <c r="G49" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>381</v>
+      </c>
+      <c r="B50" t="s">
+        <v>358</v>
+      </c>
+      <c r="C50" t="s">
+        <v>382</v>
+      </c>
+      <c r="D50" t="s">
+        <v>308</v>
+      </c>
+      <c r="E50" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
